--- a/Expense_Tracker (PROJECT) xl.xlsx
+++ b/Expense_Tracker (PROJECT) xl.xlsx
@@ -8,27 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\excel_preparation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E877475B-FBBE-42FA-BE9A-BDBBE8C5E749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2E0F699-1CD2-4BB5-B654-7137C01AF0F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{AF20B738-09BD-4AA2-9BA1-CC90A84B62BC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{AF20B738-09BD-4AA2-9BA1-CC90A84B62BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Data " sheetId="1" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" r:id="rId2"/>
-    <sheet name="Budget" sheetId="3" r:id="rId3"/>
-    <sheet name="Pivot" sheetId="7" r:id="rId4"/>
-    <sheet name="Dashboard" sheetId="5" r:id="rId5"/>
+    <sheet name="lookup" sheetId="8" r:id="rId2"/>
+    <sheet name="Summary" sheetId="2" r:id="rId3"/>
+    <sheet name="Budget" sheetId="3" r:id="rId4"/>
+    <sheet name="Pivot" sheetId="7" r:id="rId5"/>
+    <sheet name="Dashboard" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data '!$B$2:$G$50</definedName>
-    <definedName name="_xlchart.v1.0" hidden="1">Summary!$B$15:$B$19</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Summary!$C$14</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Summary!$C$15:$C$19</definedName>
     <definedName name="_xlcn.WorksheetConnection_DataB2G501" hidden="1">'Data '!$B$2:$G$50</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="48" r:id="rId6"/>
+    <pivotCache cacheId="0" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -83,7 +81,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLMDX" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
@@ -105,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="38">
   <si>
     <t>Date</t>
   </si>
@@ -205,6 +203,21 @@
   <si>
     <t>Categories over budget</t>
   </si>
+  <si>
+    <t>Category Lookup</t>
+  </si>
+  <si>
+    <t>Select Category</t>
+  </si>
+  <si>
+    <t>Total spent</t>
+  </si>
+  <si>
+    <t>xlookup</t>
+  </si>
+  <si>
+    <t>vlookup</t>
+  </si>
 </sst>
 </file>
 
@@ -247,7 +260,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -272,8 +285,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -389,25 +420,181 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -424,6 +611,26 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -647,20 +854,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="diamond"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -717,20 +911,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="square"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -787,20 +968,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="triangle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent3"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -3233,7 +3401,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{50492F63-5DCC-47EC-B4FD-20E6C7D6EF74}" name="PivotTable6" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="18">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{50492F63-5DCC-47EC-B4FD-20E6C7D6EF74}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="18">
   <location ref="A3:E10" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" allDrilled="1" showAll="0" dataSourceSort="1" defaultAttributeDrillState="1">
@@ -3737,11 +3905,11 @@
         <v>1200</v>
       </c>
       <c r="F3" s="3" t="str">
-        <f>TEXT(B3,"MMM")</f>
+        <f t="shared" ref="F3:F50" si="0">TEXT(B3,"MMM")</f>
         <v>Aug</v>
       </c>
       <c r="G3" s="3">
-        <f>MONTH(B3)</f>
+        <f t="shared" ref="G3:G50" si="1">MONTH(B3)</f>
         <v>8</v>
       </c>
     </row>
@@ -3759,11 +3927,11 @@
         <v>420</v>
       </c>
       <c r="F4" s="3" t="str">
-        <f>TEXT(B4,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Apr</v>
       </c>
       <c r="G4" s="3">
-        <f>MONTH(B4)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
@@ -3781,11 +3949,11 @@
         <v>6000</v>
       </c>
       <c r="F5" s="3" t="str">
-        <f>TEXT(B5,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Mar</v>
       </c>
       <c r="G5" s="3">
-        <f>MONTH(B5)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -3803,11 +3971,11 @@
         <v>280</v>
       </c>
       <c r="F6" s="3" t="str">
-        <f>TEXT(B6,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>May</v>
       </c>
       <c r="G6" s="3">
-        <f>MONTH(B6)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
     </row>
@@ -3825,11 +3993,11 @@
         <v>70</v>
       </c>
       <c r="F7" s="3" t="str">
-        <f>TEXT(B7,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Sep</v>
       </c>
       <c r="G7" s="3">
-        <f>MONTH(B7)</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
     </row>
@@ -3847,11 +4015,11 @@
         <v>500</v>
       </c>
       <c r="F8" s="3" t="str">
-        <f>TEXT(B8,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Sep</v>
       </c>
       <c r="G8" s="3">
-        <f>MONTH(B8)</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
     </row>
@@ -3869,11 +4037,11 @@
         <v>70</v>
       </c>
       <c r="F9" s="3" t="str">
-        <f>TEXT(B9,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Sep</v>
       </c>
       <c r="G9" s="3">
-        <f>MONTH(B9)</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
     </row>
@@ -3891,11 +4059,11 @@
         <v>3600</v>
       </c>
       <c r="F10" s="3" t="str">
-        <f>TEXT(B10,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Mar</v>
       </c>
       <c r="G10" s="3">
-        <f>MONTH(B10)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -3913,11 +4081,11 @@
         <v>3000</v>
       </c>
       <c r="F11" s="3" t="str">
-        <f>TEXT(B11,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Feb</v>
       </c>
       <c r="G11" s="3">
-        <f>MONTH(B11)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
@@ -3935,11 +4103,11 @@
         <v>120</v>
       </c>
       <c r="F12" s="3" t="str">
-        <f>TEXT(B12,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Jun</v>
       </c>
       <c r="G12" s="3">
-        <f>MONTH(B12)</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
     </row>
@@ -3957,11 +4125,11 @@
         <v>160</v>
       </c>
       <c r="F13" s="3" t="str">
-        <f>TEXT(B13,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Sep</v>
       </c>
       <c r="G13" s="3">
-        <f>MONTH(B13)</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
     </row>
@@ -3979,11 +4147,11 @@
         <v>60</v>
       </c>
       <c r="F14" s="3" t="str">
-        <f>TEXT(B14,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Aug</v>
       </c>
       <c r="G14" s="3">
-        <f>MONTH(B14)</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
     </row>
@@ -4001,11 +4169,11 @@
         <v>80</v>
       </c>
       <c r="F15" s="3" t="str">
-        <f>TEXT(B15,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Oct</v>
       </c>
       <c r="G15" s="3">
-        <f>MONTH(B15)</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
@@ -4023,11 +4191,11 @@
         <v>250</v>
       </c>
       <c r="F16" s="3" t="str">
-        <f>TEXT(B16,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Sep</v>
       </c>
       <c r="G16" s="3">
-        <f>MONTH(B16)</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
     </row>
@@ -4045,11 +4213,11 @@
         <v>5000</v>
       </c>
       <c r="F17" s="3" t="str">
-        <f>TEXT(B17,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Apr</v>
       </c>
       <c r="G17" s="3">
-        <f>MONTH(B17)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
@@ -4067,11 +4235,11 @@
         <v>600</v>
       </c>
       <c r="F18" s="3" t="str">
-        <f>TEXT(B18,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Apr</v>
       </c>
       <c r="G18" s="3">
-        <f>MONTH(B18)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
@@ -4089,11 +4257,11 @@
         <v>200</v>
       </c>
       <c r="F19" s="3" t="str">
-        <f>TEXT(B19,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>May</v>
       </c>
       <c r="G19" s="3">
-        <f>MONTH(B19)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
     </row>
@@ -4111,11 +4279,11 @@
         <v>3500</v>
       </c>
       <c r="F20" s="3" t="str">
-        <f>TEXT(B20,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Feb</v>
       </c>
       <c r="G20" s="3">
-        <f>MONTH(B20)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
@@ -4133,11 +4301,11 @@
         <v>650</v>
       </c>
       <c r="F21" s="3" t="str">
-        <f>TEXT(B21,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Sep</v>
       </c>
       <c r="G21" s="3">
-        <f>MONTH(B21)</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
     </row>
@@ -4155,11 +4323,11 @@
         <v>170</v>
       </c>
       <c r="F22" s="3" t="str">
-        <f>TEXT(B22,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Jan</v>
       </c>
       <c r="G22" s="3">
-        <f>MONTH(B22)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -4177,11 +4345,11 @@
         <v>280</v>
       </c>
       <c r="F23" s="3" t="str">
-        <f>TEXT(B23,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Mar</v>
       </c>
       <c r="G23" s="3">
-        <f>MONTH(B23)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -4199,11 +4367,11 @@
         <v>180</v>
       </c>
       <c r="F24" s="3" t="str">
-        <f>TEXT(B24,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Mar</v>
       </c>
       <c r="G24" s="3">
-        <f>MONTH(B24)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -4221,11 +4389,11 @@
         <v>80</v>
       </c>
       <c r="F25" s="3" t="str">
-        <f>TEXT(B25,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Sep</v>
       </c>
       <c r="G25" s="3">
-        <f>MONTH(B25)</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
     </row>
@@ -4243,11 +4411,11 @@
         <v>3000</v>
       </c>
       <c r="F26" s="3" t="str">
-        <f>TEXT(B26,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Mar</v>
       </c>
       <c r="G26" s="3">
-        <f>MONTH(B26)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -4265,11 +4433,11 @@
         <v>70</v>
       </c>
       <c r="F27" s="3" t="str">
-        <f>TEXT(B27,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Jul</v>
       </c>
       <c r="G27" s="3">
-        <f>MONTH(B27)</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
     </row>
@@ -4287,11 +4455,11 @@
         <v>160</v>
       </c>
       <c r="F28" s="3" t="str">
-        <f>TEXT(B28,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Jan</v>
       </c>
       <c r="G28" s="3">
-        <f>MONTH(B28)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -4309,11 +4477,11 @@
         <v>75</v>
       </c>
       <c r="F29" s="3" t="str">
-        <f>TEXT(B29,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>May</v>
       </c>
       <c r="G29" s="3">
-        <f>MONTH(B29)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
     </row>
@@ -4331,11 +4499,11 @@
         <v>100</v>
       </c>
       <c r="F30" s="3" t="str">
-        <f>TEXT(B30,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Mar</v>
       </c>
       <c r="G30" s="3">
-        <f>MONTH(B30)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -4353,11 +4521,11 @@
         <v>3000</v>
       </c>
       <c r="F31" s="3" t="str">
-        <f>TEXT(B31,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Apr</v>
       </c>
       <c r="G31" s="3">
-        <f>MONTH(B31)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
@@ -4375,11 +4543,11 @@
         <v>50</v>
       </c>
       <c r="F32" s="3" t="str">
-        <f>TEXT(B32,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Mar</v>
       </c>
       <c r="G32" s="3">
-        <f>MONTH(B32)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -4397,11 +4565,11 @@
         <v>140</v>
       </c>
       <c r="F33" s="3" t="str">
-        <f>TEXT(B33,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Jul</v>
       </c>
       <c r="G33" s="3">
-        <f>MONTH(B33)</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
     </row>
@@ -4419,11 +4587,11 @@
         <v>4000</v>
       </c>
       <c r="F34" s="3" t="str">
-        <f>TEXT(B34,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Aug</v>
       </c>
       <c r="G34" s="3">
-        <f>MONTH(B34)</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
     </row>
@@ -4441,11 +4609,11 @@
         <v>900</v>
       </c>
       <c r="F35" s="3" t="str">
-        <f>TEXT(B35,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>May</v>
       </c>
       <c r="G35" s="3">
-        <f>MONTH(B35)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
     </row>
@@ -4463,11 +4631,11 @@
         <v>300</v>
       </c>
       <c r="F36" s="3" t="str">
-        <f>TEXT(B36,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Apr</v>
       </c>
       <c r="G36" s="3">
-        <f>MONTH(B36)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
@@ -4485,11 +4653,11 @@
         <v>150</v>
       </c>
       <c r="F37" s="3" t="str">
-        <f>TEXT(B37,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Apr</v>
       </c>
       <c r="G37" s="3">
-        <f>MONTH(B37)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
@@ -4507,11 +4675,11 @@
         <v>220</v>
       </c>
       <c r="F38" s="3" t="str">
-        <f>TEXT(B38,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Jul</v>
       </c>
       <c r="G38" s="3">
-        <f>MONTH(B38)</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
     </row>
@@ -4529,11 +4697,11 @@
         <v>620</v>
       </c>
       <c r="F39" s="3" t="str">
-        <f>TEXT(B39,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Aug</v>
       </c>
       <c r="G39" s="3">
-        <f>MONTH(B39)</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
     </row>
@@ -4551,11 +4719,11 @@
         <v>250</v>
       </c>
       <c r="F40" s="3" t="str">
-        <f>TEXT(B40,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Jul</v>
       </c>
       <c r="G40" s="3">
-        <f>MONTH(B40)</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
     </row>
@@ -4573,11 +4741,11 @@
         <v>79</v>
       </c>
       <c r="F41" s="3" t="str">
-        <f>TEXT(B41,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Feb</v>
       </c>
       <c r="G41" s="3">
-        <f>MONTH(B41)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
@@ -4595,11 +4763,11 @@
         <v>120</v>
       </c>
       <c r="F42" s="3" t="str">
-        <f>TEXT(B42,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Jun</v>
       </c>
       <c r="G42" s="3">
-        <f>MONTH(B42)</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
     </row>
@@ -4617,11 +4785,11 @@
         <v>700</v>
       </c>
       <c r="F43" s="3" t="str">
-        <f>TEXT(B43,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>May</v>
       </c>
       <c r="G43" s="3">
-        <f>MONTH(B43)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
     </row>
@@ -4639,11 +4807,11 @@
         <v>4000</v>
       </c>
       <c r="F44" s="3" t="str">
-        <f>TEXT(B44,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Apr</v>
       </c>
       <c r="G44" s="3">
-        <f>MONTH(B44)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
@@ -4661,11 +4829,11 @@
         <v>210</v>
       </c>
       <c r="F45" s="3" t="str">
-        <f>TEXT(B45,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Oct</v>
       </c>
       <c r="G45" s="3">
-        <f>MONTH(B45)</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
@@ -4683,11 +4851,11 @@
         <v>3000</v>
       </c>
       <c r="F46" s="3" t="str">
-        <f>TEXT(B46,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>May</v>
       </c>
       <c r="G46" s="3">
-        <f>MONTH(B46)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
     </row>
@@ -4705,11 +4873,11 @@
         <v>599</v>
       </c>
       <c r="F47" s="3" t="str">
-        <f>TEXT(B47,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Apr</v>
       </c>
       <c r="G47" s="3">
-        <f>MONTH(B47)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
@@ -4727,11 +4895,11 @@
         <v>450</v>
       </c>
       <c r="F48" s="3" t="str">
-        <f>TEXT(B48,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Mar</v>
       </c>
       <c r="G48" s="3">
-        <f>MONTH(B48)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -4749,11 +4917,11 @@
         <v>500</v>
       </c>
       <c r="F49" s="3" t="str">
-        <f>TEXT(B49,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>Sep</v>
       </c>
       <c r="G49" s="3">
-        <f>MONTH(B49)</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
     </row>
@@ -4771,11 +4939,11 @@
         <v>1280</v>
       </c>
       <c r="F50" s="3" t="str">
-        <f>TEXT(B50,"MMM")</f>
+        <f t="shared" si="0"/>
         <v>May</v>
       </c>
       <c r="G50" s="3">
-        <f>MONTH(B50)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
     </row>
@@ -4806,6 +4974,134 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7502D250-90B1-4704-B494-241542E0D47C}">
+  <dimension ref="B2:F10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="15.1796875" customWidth="1"/>
+    <col min="3" max="3" width="12.7265625" customWidth="1"/>
+    <col min="4" max="4" width="13.81640625" customWidth="1"/>
+    <col min="5" max="5" width="10.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B2" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+    </row>
+    <row r="4" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="31"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="25"/>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B5" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="27">
+        <f>_xlfn.XLOOKUP($C$4,Summary!B15:B19,Summary!C15:C19)</f>
+        <v>38100</v>
+      </c>
+      <c r="D5" s="32">
+        <f>VLOOKUP(C4,Summary!B15:E19,2,FALSE)</f>
+        <v>38100</v>
+      </c>
+      <c r="E5" s="26"/>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B6" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="28">
+        <f>_xlfn.XLOOKUP($C$4,Summary!$B$15:$B$19,Summary!$D$15:$D$19)</f>
+        <v>10</v>
+      </c>
+      <c r="D6" s="33">
+        <f>VLOOKUP(C4,Summary!B15:E19,3,FALSE)</f>
+        <v>10</v>
+      </c>
+      <c r="E6" s="26"/>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B7" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="28">
+        <f>ROUND(_xlfn.XLOOKUP($C$4,Summary!$B$15:$B$19,Summary!$E$15:$E$19),0)</f>
+        <v>3810</v>
+      </c>
+      <c r="D7" s="33">
+        <f>VLOOKUP(C4,Summary!B15:E19,4,FALSE)</f>
+        <v>3810</v>
+      </c>
+      <c r="E7" s="26"/>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B8" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="28">
+        <f>_xlfn.XLOOKUP($C$4,Budget!$B$3:$B$7,Budget!$C$3:$C$7)</f>
+        <v>30000</v>
+      </c>
+      <c r="D8" s="33">
+        <f>VLOOKUP(C4,Budget!B3:C7,2,FALSE)</f>
+        <v>30000</v>
+      </c>
+      <c r="E8" s="26"/>
+    </row>
+    <row r="9" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="29" t="str">
+        <f>_xlfn.XLOOKUP(lookup!$C$4,Budget!$B$3:$B$7,Budget!$F$3:$F$7)</f>
+        <v>Over Budget</v>
+      </c>
+      <c r="D9" s="34" t="str">
+        <f>VLOOKUP(C4,Budget!B3:F7,5,FALSE)</f>
+        <v>Over Budget</v>
+      </c>
+      <c r="E9" s="26"/>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2C3F2EE2-F9C4-4B98-9571-0DE36E9BD25A}">
+          <x14:formula1>
+            <xm:f>Summary!$B$15:$B$19</xm:f>
+          </x14:formula1>
+          <xm:sqref>C4</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72D41AED-C6C9-4854-A2F2-2F43E5DC815B}">
   <dimension ref="B2:E19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4819,90 +5115,82 @@
   <sheetData>
     <row r="2" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="10">
         <f>SUM('Data '!E3:E50)</f>
         <v>50443</v>
       </c>
     </row>
-    <row r="4" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C4" s="4"/>
-    </row>
+    <row r="4" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="5" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="10">
         <f>AVERAGE('Data '!E3:E50)</f>
         <v>1050.8958333333333</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C6" s="4"/>
-    </row>
+    <row r="6" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="7" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="10">
         <f>MAX('Data '!E3:E50)</f>
         <v>6000</v>
       </c>
     </row>
-    <row r="8" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C8" s="4"/>
-    </row>
+    <row r="8" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="9" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="10">
         <f>MIN('Data '!E3:E50)</f>
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C10" s="4"/>
-    </row>
+    <row r="10" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="11" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="9">
         <f>COUNT('Data '!E3:E50)</f>
         <v>48</v>
       </c>
     </row>
     <row r="13" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="16" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="11">
         <f>SUMIF('Data '!$C$3:$C$50,Summary!B15,'Data '!$E$3:$E$50)</f>
         <v>2220</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="11">
         <f>COUNTIF('Data '!$C$3:$C$50,Summary!B15)</f>
         <v>10</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="11">
         <f>AVERAGEIF('Data '!$C$3:$C$50,Summary!B15,'Data '!$E$3:$E$50)</f>
         <v>222</v>
       </c>
@@ -4980,7 +5268,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{473A6791-44E2-4133-83DC-CD1C66235FF6}">
   <dimension ref="B2:F7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4992,19 +5280,19 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="8" t="s">
         <v>22</v>
       </c>
     </row>
@@ -5121,7 +5409,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A1D3193-05CC-4462-9950-F7FBC7CCB8C8}">
   <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -5133,7 +5421,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B1" t="s" vm="1">
@@ -5141,15 +5429,15 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>26</v>
       </c>
       <c r="B4" t="s">
@@ -5166,102 +5454,101 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7">
+      <c r="C5">
         <v>1160</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5">
         <v>1060</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5">
         <v>2220</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6">
         <v>500</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6">
         <v>250</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6">
         <v>780</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6">
         <v>1530</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7">
         <v>12000</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7">
         <v>10100</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7">
         <v>16000</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7">
         <v>38100</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8">
         <v>1799</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8">
         <v>804</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8">
         <v>320</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8">
         <v>2923</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9">
         <v>2150</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9">
         <v>810</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9">
         <v>2710</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9">
         <v>5670</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10">
         <v>16449</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10">
         <v>13124</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10">
         <v>20870</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10">
         <v>50443</v>
       </c>
     </row>
@@ -5270,9 +5557,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1E2E16-B81E-4532-BBFE-2AC5F184564A}">
-  <dimension ref="B4:G9"/>
+  <dimension ref="C4:G9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="12.7265625" customWidth="1"/>
@@ -5283,50 +5570,49 @@
     <col min="7" max="7" width="15.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="F4" s="9" t="s">
+    <row r="4" spans="3:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="F4" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="9"/>
-    </row>
-    <row r="5" spans="2:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-    </row>
-    <row r="6" spans="2:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="F6" s="10" t="s">
+      <c r="G4" s="17"/>
+    </row>
+    <row r="5" spans="3:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+    </row>
+    <row r="6" spans="3:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="F6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="7">
         <f>Summary!C3</f>
         <v>50443</v>
       </c>
     </row>
-    <row r="7" spans="2:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="F7" s="10" t="s">
+    <row r="7" spans="3:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="F7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="7">
         <f>ROUND(Summary!C5,0)</f>
         <v>1051</v>
       </c>
     </row>
-    <row r="8" spans="2:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="B8" s="4"/>
-      <c r="C8" s="8"/>
-      <c r="F8" s="10" t="s">
+    <row r="8" spans="3:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="C8" s="6"/>
+      <c r="F8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="7">
         <f>Summary!C11</f>
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="2:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="F9" s="10" t="s">
+    <row r="9" spans="3:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="F9" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="7">
         <f>COUNTIF(Budget!F3:F7,"Over Budget")</f>
         <v>3</v>
       </c>
